--- a/processed_ruby_restored_xlsx/sc232_凛４：ゲーム中.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc232_凛４：ゲーム中.ss.xlsx
@@ -608,7 +608,8 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>So yeah, I'm here by myself, killing time in the room.</t>
+          <t>So yeah, I'm here by myself, killing time in the
+room.</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -669,8 +670,8 @@
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>Thinking that made fiddling with my phone feel stupid,
-which only made me feel even more bored.</t>
+          <t>Thinking that made fiddling with my phone feel
+stupid, which only made me feel even more bored.</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -777,7 +778,8 @@
       <c r="B21" s="1" t="inlineStr">
         <is>
           <t>...When I realized I didn't remember anything after
-lying down, it seemed I'd been overcome by sleepiness.</t>
+lying down, it seemed I'd been overcome by
+sleepiness.</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -959,8 +961,8 @@
       </c>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>Not only that, but she had her upper body resting on a
-rolled-up pillow and sheets.</t>
+          <t>Not only that, but she had her upper body resting on
+a rolled-up pillow and sheets.</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1307,8 +1309,8 @@
       </c>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>While Miru-chan is doing it, making little noises like
-“ooh” and “huh,” Rin-chan is completely silent.</t>
+          <t>While Miru-chan is doing it, making little noises
+like “ooh” and “huh,” Rin-chan is completely silent.</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -1339,8 +1341,8 @@
       </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>That said, if I just called out normally, she probably
-wouldn't pay any attention to me….</t>
+          <t>That said, if I just called out normally, she
+probably wouldn't pay any attention to me….</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -1553,8 +1555,8 @@
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>Ugh...！ Even if she's totally absorbed, saying it like
-that is a bit much...</t>
+          <t>Ugh...！ Even if she's totally absorbed, saying it
+like that is a bit much...</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -1569,8 +1571,8 @@
       </c>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t>Alright, if Rin-chan intends to be like this, I'll win
-her over my way！</t>
+          <t>Alright, if Rin-chan intends to be like this, I'll
+win her over my way！</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -2088,8 +2090,8 @@
       </c>
       <c r="B107" s="1" t="inlineStr">
         <is>
-          <t>When I grabbed her butt firmly, Rin-chan's back gave a
-little jolt.</t>
+          <t>When I grabbed her butt firmly, Rin-chan's back gave
+a little jolt.</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -3156,7 +3158,8 @@
       </c>
       <c r="B177" s="1" t="inlineStr">
         <is>
-          <t>When the stage starts, she stops looking my way again.</t>
+          <t>When the stage starts, she stops looking my way
+again.</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -3353,9 +3356,9 @@
       </c>
       <c r="B190" s="1" t="inlineStr">
         <is>
-          <t>The crotch is the part that presses against the groove
-between her legs, so being stroked there probably hits
-her hard.</t>
+          <t>The crotch is the part that presses against the
+groove between her legs, so being stroked there
+probably hits her hard.</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -3861,8 +3864,8 @@
       <c r="B223" s="1" t="inlineStr">
         <is>
           <t>I kept alternating between scolding like a
-life-guidance teacher and acting spoiled to get her to
-turn.</t>
+life-guidance teacher and acting spoiled to get her
+to turn.</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -3952,7 +3955,8 @@
       </c>
       <c r="B229" s="1" t="inlineStr">
         <is>
-          <t>As proof of that, I could feel warmth at the crotch...</t>
+          <t>As proof of that, I could feel warmth at the
+crotch...</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -3997,8 +4001,8 @@
       </c>
       <c r="B232" s="1" t="inlineStr">
         <is>
-          <t>The moment I pressed my finger against the crotch, her
-breaths became frantic.</t>
+          <t>The moment I pressed my finger against the crotch,
+her breaths became frantic.</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -4349,8 +4353,8 @@
       </c>
       <c r="B255" s="1" t="inlineStr">
         <is>
-          <t>Her attitude was as cold as ever, but I could feel her
-body scent growing stronger.</t>
+          <t>Her attitude was as cold as ever, but I could feel
+her body scent growing stronger.</t>
         </is>
       </c>
       <c r="C255" t="n">
@@ -4365,7 +4369,8 @@
       </c>
       <c r="B256" s="1" t="inlineStr">
         <is>
-          <t>A rich, cheesy-mousse-like aroma was wafting thickly…！</t>
+          <t>A rich, cheesy-mousse-like aroma was wafting
+thickly…！</t>
         </is>
       </c>
       <c r="C256" t="n">
@@ -4746,7 +4751,8 @@
       </c>
       <c r="B281" s="1" t="inlineStr">
         <is>
-          <t>But having come this far, I can't hold back anymore...</t>
+          <t>But having come this far, I can't hold back
+anymore...</t>
         </is>
       </c>
       <c r="C281" t="n">
@@ -4959,7 +4965,8 @@
       </c>
       <c r="B295" s="1" t="inlineStr">
         <is>
-          <t>「R-Rin-chan's inside just suddenly feels so intense…？」</t>
+          <t>「R-Rin-chan's inside just suddenly feels so
+intense…？」</t>
         </is>
       </c>
       <c r="C295" t="n">
@@ -5019,8 +5026,8 @@
       </c>
       <c r="B299" s="1" t="inlineStr">
         <is>
-          <t>「So that means you got turned on from having your butt
-groped, huh？」</t>
+          <t>「So that means you got turned on from having your
+butt groped, huh？」</t>
         </is>
       </c>
       <c r="C299" t="n">
@@ -5171,8 +5178,8 @@
       </c>
       <c r="B309" s="1" t="inlineStr">
         <is>
-          <t>She brusquely turns me down, but I can feel a response
-in her hesitant voice.</t>
+          <t>She brusquely turns me down, but I can feel a
+response in her hesitant voice.</t>
         </is>
       </c>
       <c r="C309" t="n">
@@ -5694,7 +5701,8 @@
       </c>
       <c r="B343" s="1" t="inlineStr">
         <is>
-          <t>「k... u, n！ nfu... fuh, fuh！ uh... ku！ fuh, fuh, fuu！」</t>
+          <t>「k... u, n！ nfu... fuh, fuh！ uh... ku！ fuh, fuh,
+fuu！」</t>
         </is>
       </c>
       <c r="C343" t="n">
@@ -5922,8 +5930,8 @@
       </c>
       <c r="B358" s="1" t="inlineStr">
         <is>
-          <t>Feeling good about that, I start driving long strokes,
-thrusting into her vagina.</t>
+          <t>Feeling good about that, I start driving long
+strokes, thrusting into her vagina.</t>
         </is>
       </c>
       <c r="C358" t="n">
@@ -6139,7 +6147,8 @@
       </c>
       <c r="B372" s="1" t="inlineStr">
         <is>
-          <t>While I was thrusting away, Rin-chan called out to me.</t>
+          <t>While I was thrusting away, Rin-chan called out to
+me.</t>
         </is>
       </c>
       <c r="C372" t="n">
@@ -6260,7 +6269,8 @@
       </c>
       <c r="B380" s="1" t="inlineStr">
         <is>
-          <t>When I whispered softly, an irritated reply came back.</t>
+          <t>When I whispered softly, an irritated reply came
+back.</t>
         </is>
       </c>
       <c r="C380" t="n">
@@ -6399,8 +6409,8 @@
       </c>
       <c r="B389" s="1" t="inlineStr">
         <is>
-          <t>Thrusting became easier, and her vaginal folds rustled
-as they wound around mine penis.</t>
+          <t>Thrusting became easier, and her vaginal folds
+rustled as they wound around mine penis.</t>
         </is>
       </c>
       <c r="C389" t="n">
@@ -6506,8 +6516,8 @@
       <c r="B396" s="1" t="inlineStr">
         <is>
           <t>I've been pretending to be distant until now, so even
-if it feels good, I guess I have no choice but to keep
-doing that….</t>
+if it feels good, I guess I have no choice but to
+keep doing that….</t>
         </is>
       </c>
       <c r="C396" t="n">
@@ -6583,8 +6593,8 @@
       </c>
       <c r="B401" s="1" t="inlineStr">
         <is>
-          <t>I speed up my thrusting and rub her insides full of my
-penis, Rin-chan.</t>
+          <t>I speed up my thrusting and rub her insides full of
+my penis, Rin-chan.</t>
         </is>
       </c>
       <c r="C401" t="n">
@@ -7043,8 +7053,8 @@
       </c>
       <c r="B431" s="1" t="inlineStr">
         <is>
-          <t>Even when I stop moving my hips, the stimulation on my
-penis doesn't stop.</t>
+          <t>Even when I stop moving my hips, the stimulation on
+my penis doesn't stop.</t>
         </is>
       </c>
       <c r="C431" t="n">
@@ -7198,7 +7208,8 @@
       </c>
       <c r="B441" s="1" t="inlineStr">
         <is>
-          <t>When I asked casually, I finally got an honest answer.</t>
+          <t>When I asked casually, I finally got an honest
+answer.</t>
         </is>
       </c>
       <c r="C441" t="n">
@@ -7273,8 +7284,8 @@
       </c>
       <c r="B446" s="1" t="inlineStr">
         <is>
-          <t>When the thrusting resumed, Rin-chan's voice burst out
-immediately.</t>
+          <t>When the thrusting resumed, Rin-chan's voice burst
+out immediately.</t>
         </is>
       </c>
       <c r="C446" t="n">
@@ -7335,8 +7346,8 @@
       </c>
       <c r="B450" s="1" t="inlineStr">
         <is>
-          <t>Because we're consciously moving together, it's turned
-into an incredibly deep union.</t>
+          <t>Because we're consciously moving together, it's
+turned into an incredibly deep union.</t>
         </is>
       </c>
       <c r="C450" t="n">
@@ -7443,8 +7454,8 @@
       </c>
       <c r="B457" s="1" t="inlineStr">
         <is>
-          <t>When I think she's trying so hard to accommodate me, I
-just can't help my penis from trembling！</t>
+          <t>When I think she's trying so hard to accommodate me,
+I just can't help my penis from trembling！</t>
         </is>
       </c>
       <c r="C457" t="n">
@@ -7794,8 +7805,8 @@
       </c>
       <c r="B480" s="1" t="inlineStr">
         <is>
-          <t>Pulled along by Rin-chan's climax, I thrust my hips in
-as if seizing the moment...！</t>
+          <t>Pulled along by Rin-chan's climax, I thrust my hips
+in as if seizing the moment...！</t>
         </is>
       </c>
       <c r="C480" t="n">
@@ -8588,8 +8599,8 @@
       </c>
       <c r="B532" s="1" t="inlineStr">
         <is>
-          <t>Somehow… it looks like it’s coming out a lot more than
-usual…！</t>
+          <t>Somehow… it looks like it’s coming out a lot more
+than usual…！</t>
         </is>
       </c>
       <c r="C532" t="n">
@@ -8635,8 +8646,8 @@
       <c r="B535" s="1" t="inlineStr">
         <is>
           <t>Rin-chan, who had reached climax and was still
-breathing heavily, seemed to feel something odd in her
-butt and turned her teary eyes toward me.</t>
+breathing heavily, seemed to feel something odd in
+her butt and turned her teary eyes toward me.</t>
         </is>
       </c>
       <c r="C535" t="n">
@@ -8927,8 +8938,9 @@
       </c>
       <c r="B554" s="1" t="inlineStr">
         <is>
-          <t>...Now that I got all worked up and things had started
-to spiral, perhaps this is a good opportunity.</t>
+          <t>...Now that I got all worked up and things had
+started to spiral, perhaps this is a good
+opportunity.</t>
         </is>
       </c>
       <c r="C554" t="n">
@@ -8958,8 +8970,8 @@
       </c>
       <c r="B556" s="1" t="inlineStr">
         <is>
-          <t>「You wouldn't turn to me, Rin-chan, so I got lonely...
-I'm sorry, okay？」</t>
+          <t>「You wouldn't turn to me, Rin-chan, so I got
+lonely... I'm sorry, okay？」</t>
         </is>
       </c>
       <c r="C556" t="n">
@@ -9541,8 +9553,8 @@
       </c>
       <c r="B594" s="1" t="inlineStr">
         <is>
-          <t>As I wondered what to say, Rin-chan gave me a sidelong
-look.</t>
+          <t>As I wondered what to say, Rin-chan gave me a
+sidelong look.</t>
         </is>
       </c>
       <c r="C594" t="n">

--- a/processed_ruby_restored_xlsx/sc232_凛４：ゲーム中.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc232_凛４：ゲーム中.ss.xlsx
@@ -1341,7 +1341,7 @@
       </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>That said, if I just called out normally, she
+          <t>That said, if I just called out normally, they
 probably wouldn't pay any attention to me….</t>
         </is>
       </c>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="B105" s="1" t="inlineStr">
         <is>
-          <t>Rin</t>
+          <t>Rin-chan</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="B108" s="1" t="inlineStr">
         <is>
-          <t>Rin</t>
+          <t>Rin-chan</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="B113" s="1" t="inlineStr">
         <is>
-          <t>Rin</t>
+          <t>Rin-chan</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="B119" s="1" t="inlineStr">
         <is>
-          <t>Rin</t>
+          <t>Rin-chan</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="B126" s="1" t="inlineStr">
         <is>
-          <t>Rin</t>
+          <t>Rin-chan</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="B134" s="1" t="inlineStr">
         <is>
-          <t>Rin</t>
+          <t>Rin-chan</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="B138" s="1" t="inlineStr">
         <is>
-          <t>Saying that, I give her another smack on the butt.</t>
+          <t>Saying that, he gives her another smack on the butt.</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="B142" s="1" t="inlineStr">
         <is>
-          <t>I'm spanking her over her panties, so it probably
+          <t>He's spanking her over her panties, so it probably
 doesn't hurt that much.</t>
         </is>
       </c>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="B147" s="1" t="inlineStr">
         <is>
-          <t>She's ignoring me again... completely stubborn.</t>
+          <t>She's ignoring him again... completely stubborn.</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -4079,7 +4079,7 @@
       </c>
       <c r="B237" s="1" t="inlineStr">
         <is>
-          <t>「…ah…ahh…ahhh—！」</t>
+          <t>…ah…ahh…ahhh—！</t>
         </is>
       </c>
       <c r="C237" t="n">
@@ -5087,8 +5087,8 @@
       </c>
       <c r="B303" s="1" t="inlineStr">
         <is>
-          <t>Because she acted like she was ignoring me, maybe she
-thought she had to keep up that act？</t>
+          <t>Because they acted like they were ignoring me, maybe
+they thought they had to keep up that act？</t>
         </is>
       </c>
       <c r="C303" t="n">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="B339" s="1" t="inlineStr">
         <is>
-          <t>「Nnngh... yaah, ah, aaah！ Ah... k！」</t>
+          <t>Nnngh... yaah, ah, aaah！ Ah... k！</t>
         </is>
       </c>
       <c r="C339" t="n">
@@ -5701,8 +5701,7 @@
       </c>
       <c r="B343" s="1" t="inlineStr">
         <is>
-          <t>「k... u, n！ nfu... fuh, fuh！ uh... ku！ fuh, fuh,
-fuu！」</t>
+          <t>k... u, n！ nfu... fuh, fuh！ uh... ku！ fuh, fuh, fuu！</t>
         </is>
       </c>
       <c r="C343" t="n">
@@ -5961,7 +5960,7 @@
       </c>
       <c r="B360" s="1" t="inlineStr">
         <is>
-          <t>「Nn... nnnn！？ Ah, ah！ A... fua！？ Uku, kuuuu...！」</t>
+          <t>Nn... nnnn！？ Ah, ah！ A... fua！？ Uku, kuuuu...！</t>
         </is>
       </c>
       <c r="C360" t="n">
@@ -6039,8 +6038,8 @@
       </c>
       <c r="B365" s="1" t="inlineStr">
         <is>
-          <t>「Haa！ Nnngh！ Ah！ Ah！ It's... it's so... digging in...
-my stomach... Uuuu！」</t>
+          <t>Haa！ Nnngh！ Ah！ Ah！ It's... it's so... digging in...
+my stomach... Uuuu！</t>
         </is>
       </c>
       <c r="C365" t="n">
@@ -6410,7 +6409,7 @@
       <c r="B389" s="1" t="inlineStr">
         <is>
           <t>Thrusting became easier, and her vaginal folds
-rustled as they wound around mine penis.</t>
+rustled as they wound around his penis.</t>
         </is>
       </c>
       <c r="C389" t="n">
@@ -6577,8 +6576,8 @@
       </c>
       <c r="B400" s="1" t="inlineStr">
         <is>
-          <t>「Ugh... uuh... nnaah！ Ah, ah-ah！ Ki... kimo-hi... it
-doesn't feel good！ Ku, uuu...！」</t>
+          <t>Ugh... uuh... nnaah！ Ah, ah-ah！ Ki... kimo-hi... it
+doesn't feel good！ Ku, uuu...！</t>
         </is>
       </c>
       <c r="C400" t="n">
@@ -7423,8 +7422,8 @@
       </c>
       <c r="B455" s="1" t="inlineStr">
         <is>
-          <t>「Ah! Ah! Yes... that's good! Yes! Fuhyuu... fuh, uuh!
-N-no... ah!」</t>
+          <t>Ah! Ah! Yes... that's good! Yes! Fuhyuu... fuh, uuh!
+N-no... ah!</t>
         </is>
       </c>
       <c r="C455" t="n">
@@ -7454,8 +7453,8 @@
       </c>
       <c r="B457" s="1" t="inlineStr">
         <is>
-          <t>When I think she's trying so hard to accommodate me,
-I just can't help my penis from trembling！</t>
+          <t>When I think they're trying so hard to accommodate
+me, I just can't help my penis from trembling！</t>
         </is>
       </c>
       <c r="C457" t="n">
@@ -8171,8 +8170,8 @@
       </c>
       <c r="B504" s="1" t="inlineStr">
         <is>
-          <t>…Keeping my connection, I steadied my breathing, and
-when I calmed down I pulled my penis out.</t>
+          <t>…Keeping his connection, he steadied his breathing,
+and when he calmed down he pulled his penis out.</t>
         </is>
       </c>
       <c r="C504" t="n">
@@ -8232,7 +8231,7 @@
       </c>
       <c r="B508" s="1" t="inlineStr">
         <is>
-          <t>When my penis came free, Rin-chan let out a cute
+          <t>When his penis came free, Rin-chan let out a cute
 little sound and squeezed her butt muscles tight.</t>
         </is>
       </c>
@@ -8248,7 +8247,7 @@
       </c>
       <c r="B509" s="1" t="inlineStr">
         <is>
-          <t>It was as if she were trying not to spill my cum…</t>
+          <t>It was as if she were trying not to spill his cum…</t>
         </is>
       </c>
       <c r="C509" t="n">
@@ -8447,7 +8446,7 @@
       </c>
       <c r="B522" s="1" t="inlineStr">
         <is>
-          <t>「Nn！？ Nfuuu...！ Uwa... waaah...！ Ah...！ Awaa...！」</t>
+          <t>Nn！？ Nfuuu...！ Uwa... waaah...！ Ah...！ Awaa...！</t>
         </is>
       </c>
       <c r="C522" t="n">
@@ -8970,8 +8969,8 @@
       </c>
       <c r="B556" s="1" t="inlineStr">
         <is>
-          <t>「You wouldn't turn to me, Rin-chan, so I got
-lonely... I'm sorry, okay？」</t>
+          <t>You wouldn't turn to me, Rin-chan, so I got lonely...
+I'm sorry, okay？</t>
         </is>
       </c>
       <c r="C556" t="n">
